--- a/output/2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -489,10 +489,9 @@
           <t>info@metal-kovis.hr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -527,10 +526,9 @@
           <t>info@celada.com.hr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -565,10 +563,9 @@
           <t>info@jurcec.hr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -598,7 +595,6 @@
           <t>01/6216001</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Sito web individuato tramite ricerca web (assente nella lista grezza originale); noleggio e vendita utensili/macchine</t>
@@ -606,7 +602,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -616,7 +612,6 @@
           <t>PROGRESIVA AIPO d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Velika Gorica</t>
@@ -632,7 +627,6 @@
           <t>01/6221619</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Nessun sito web reperito</t>
@@ -650,7 +644,6 @@
           <t>DANICI d.o.o.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Velika Gorica</t>
@@ -666,7 +659,6 @@
           <t>01/6218625</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Telefono e indirizzo (Majurčeva 27) reperiti tramite ricerca web; nessun sito/e-mail trovati</t>
@@ -674,7 +666,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -709,7 +701,6 @@
           <t>info@art-visum.hr</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>DA VERIFICARE UMANAMENTE</t>
@@ -754,7 +745,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -784,7 +775,6 @@
           <t>+385 (0)1 6294 304</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Produttore e grossista di utensili di precisione (diamantati, a profilo speciale) dal 1991; sito e telefono reperiti tramite ricerca web, assenti nella lista grezza originale</t>
@@ -792,7 +782,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -834,7 +824,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -876,7 +866,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -918,7 +908,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -948,7 +938,6 @@
           <t>01 66 22 820</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Sede a Zagabria città, non nella Zagrebačka županija in senso stretto</t>
@@ -956,7 +945,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -998,7 +987,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1017,6 @@
           <t>+385 1 3777964</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Sede a Zagabria città, non nella Zagrebačka županija in senso stretto</t>
@@ -1036,7 +1024,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1066,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1096,6 @@
           <t>01 2985626</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Sede a Zagabria città, non nella Zagrebačka županija in senso stretto</t>
@@ -1116,7 +1103,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1145,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
